--- a/generation_zy/hiwo-物料1-1.xlsx
+++ b/generation_zy/hiwo-物料1-1.xlsx
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>NCc1ccccc1</t>
+          <t>Cc1csc(=S)s1</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Fc1ccccn1</t>
+          <t>Cc1csc(=S)s1</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>O=C1CCC(=O)N1Br</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,GDME</t>
+          <t>triethylamine</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,toluene</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,GDME</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,toluene</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,toluene</t>
+          <t>tetrahydrofuran</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,1,4-dioxane</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,toluene</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>溶剂1,(2)H8-toluene</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>triethylamine</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>dichloromethane</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>空</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
